--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOSCONES CORRALEJO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOSCONES CORRALEJO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. JOAO</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>14.0525</v>
+        <v>12.5112</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0736</v>
+        <v>9.4278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9787999999999997</v>
+        <v>3.0835</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8265</v>
+        <v>1.285999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5236</v>
+        <v>3.1171</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.6972</v>
+        <v>-1.831</v>
       </c>
       <c r="J2" t="n">
-        <v>10.659</v>
+        <v>8.292999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9.1126</v>
+        <v>4.7069</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5464</v>
+        <v>3.5858</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.8326</v>
+        <v>-7.0068</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.589</v>
+        <v>-1.5899</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.2435</v>
+        <v>-5.4168</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.7032</v>
+        <v>4.2477</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9.6539</v>
+        <v>-4.0547</v>
       </c>
       <c r="R2" t="n">
-        <v>6.9508</v>
+        <v>8.3024</v>
       </c>
       <c r="S2" t="n">
-        <v>12.2573</v>
+        <v>3.7028</v>
       </c>
       <c r="T2" t="n">
-        <v>9.126999999999999</v>
+        <v>1.5492</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1301</v>
+        <v>2.1538</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3283</v>
+        <v>3.2747</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9413</v>
+        <v>3.6405</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.2696</v>
+        <v>-0.3657000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>A. JOAO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>13.034</v>
+        <v>7.091</v>
       </c>
       <c r="E3" t="n">
-        <v>9.668899999999999</v>
+        <v>7.240799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3652</v>
+        <v>-0.1497999999999997</v>
       </c>
       <c r="G3" t="n">
-        <v>1.285999999999999</v>
+        <v>4.8265</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1171</v>
+        <v>7.5236</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.831</v>
+        <v>-2.6972</v>
       </c>
       <c r="J3" t="n">
-        <v>8.292999999999999</v>
+        <v>10.659</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7069</v>
+        <v>9.1126</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5858</v>
+        <v>1.5464</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.0068</v>
+        <v>-5.8326</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5899</v>
+        <v>-1.589</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.4168</v>
+        <v>-4.2435</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2477</v>
+        <v>-2.7032</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0547</v>
+        <v>-9.6539</v>
       </c>
       <c r="R3" t="n">
-        <v>8.3024</v>
+        <v>6.9508</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2256</v>
+        <v>5.2958</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7902</v>
+        <v>3.2944</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4355</v>
+        <v>2.0016</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2747</v>
+        <v>-0.3283</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6405</v>
+        <v>2.9413</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3657000000000001</v>
+        <v>-3.2696</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>G. FIGUEROA ALEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7748</v>
+        <v>0.5034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7187999999999994</v>
+        <v>0.1448</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0559</v>
+        <v>0.3586</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8224</v>
+        <v>0.3172</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6891</v>
+        <v>0.0414</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1333000000000001</v>
+        <v>0.2758</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.9099</v>
+        <v>0.0414</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9981</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08820000000000006</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0875</v>
+        <v>0.2758</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3093</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2216</v>
+        <v>0.2758</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1930000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7378</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5892</v>
+        <v>0.1862</v>
       </c>
       <c r="T4" t="n">
-        <v>4.273899999999999</v>
+        <v>0.1034</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3152</v>
+        <v>0.0828</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. FIGUEROA ALEMAN</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3503</v>
+        <v>-0.4287000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0414</v>
+        <v>-1.7081</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3089</v>
+        <v>1.2794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3172</v>
+        <v>-0.8224</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0414</v>
+        <v>-0.6891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2758</v>
+        <v>-0.1333000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0414</v>
+        <v>-1.9099</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>-1.9981</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.08820000000000006</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2758</v>
+        <v>1.0875</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.3093</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2758</v>
+        <v>-0.2216</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1930000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.7378</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0331</v>
+        <v>2.3858</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.847</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0331</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.0845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. TSHIMANGA ZOLA</t>
+          <t>J. BAEZ CARRERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6215000000000002</v>
+        <v>-1.0774</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1827000000000001</v>
+        <v>0.1021</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8044</v>
+        <v>-1.1794</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6458</v>
+        <v>-1.0498</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6615</v>
+        <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01569999999999999</v>
+        <v>-1.1394</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0372</v>
+        <v>0.1021</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2814</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2442</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6087</v>
+        <v>-1.1519</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3801</v>
+        <v>0.0689</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2285</v>
+        <v>-1.2208</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3862000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9969</v>
+        <v>-0.0275</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7646</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2324</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4135</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BAEZ CARRERAS</t>
+          <t>L. BLANCO CENTENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,67 +952,67 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.978</v>
+        <v>-1.4144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1021</v>
+        <v>-4.2121</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0801</v>
+        <v>2.7977</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0498</v>
+        <v>-0.3417000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0896</v>
+        <v>-0.5383000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1394</v>
+        <v>0.1966000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1021</v>
+        <v>0.5577000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0207</v>
+        <v>-0.2608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>0.8184999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1519</v>
+        <v>-0.8993000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0689</v>
+        <v>-0.2775000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2208</v>
+        <v>-0.6216999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.317</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.2131</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8962</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0718</v>
+        <v>0.9586</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.1577</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0718</v>
+        <v>0.8008</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BLANCO CENTENO</t>
+          <t>K. TSHIMANGA ZOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4575</v>
+        <v>-1.8046</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9571</v>
+        <v>-0.8514999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4996</v>
+        <v>-0.9534</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3417000000000001</v>
+        <v>-2.6458</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5383000000000001</v>
+        <v>-2.6615</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1966000000000001</v>
+        <v>0.01569999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5577000000000001</v>
+        <v>-1.0372</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2608</v>
+        <v>-1.2814</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8184999999999999</v>
+        <v>0.2442</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8993000000000001</v>
+        <v>-1.6087</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2775000000000001</v>
+        <v>-1.3801</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6216999999999999</v>
+        <v>-0.2285</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.317</v>
+        <v>-0.3862000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.2131</v>
+        <v>-1.1585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9157</v>
+        <v>0.8138000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4128000000000001</v>
+        <v>0.7304</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5029999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2856</v>
+        <v>0.4135</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>J. BARRIOS RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6376</v>
+        <v>-4.571099999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.7418</v>
+        <v>-5.12</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1041</v>
+        <v>0.5486</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.3513</v>
+        <v>-3.6316</v>
       </c>
       <c r="H9" t="n">
-        <v>-14.8111</v>
+        <v>-2.3519</v>
       </c>
       <c r="I9" t="n">
-        <v>4.46</v>
+        <v>-1.2794</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.445</v>
+        <v>-2.9749</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.1504</v>
+        <v>-1.7994</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7055</v>
+        <v>-1.1755</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.9062</v>
+        <v>-0.6565</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.6609</v>
+        <v>-0.5525</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7546999999999999</v>
+        <v>-0.1039</v>
       </c>
       <c r="P9" t="n">
-        <v>5.4061</v>
+        <v>0.5792999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.8817</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>14.2878</v>
+        <v>2.5101</v>
       </c>
       <c r="S9" t="n">
-        <v>4.9754</v>
+        <v>-0.0484000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>4.74</v>
+        <v>-0.2142</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2353000000000002</v>
+        <v>0.1659</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.6678</v>
+        <v>-1.4707</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.1552</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5126</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BARRIOS RUIZ</t>
+          <t>D. CABRERA CABRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.036</v>
+        <v>-6.0728</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4854</v>
+        <v>-2.5465</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4491999999999998</v>
+        <v>-3.5263</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6316</v>
+        <v>-4.567299999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3519</v>
+        <v>-2.2343</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2794</v>
+        <v>-2.3332</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9749</v>
+        <v>-2.2204</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7994</v>
+        <v>-0.9228</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1755</v>
+        <v>-1.2976</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6565</v>
+        <v>-2.3469</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5525</v>
+        <v>-1.3114</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1039</v>
+        <v>-1.0356</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5792999999999999</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5101</v>
+        <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5130999999999999</v>
+        <v>-0.1933</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5797000000000001</v>
+        <v>0.2612</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06659999999999999</v>
+        <v>-0.4543999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4707</v>
+        <v>-2.0845</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4707</v>
+        <v>-2.6557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CABRERA CABRERA</t>
+          <t>A. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5379</v>
+        <v>-7.2317</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5124</v>
+        <v>-12.9766</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0255</v>
+        <v>5.7449</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.567299999999999</v>
+        <v>-10.1469</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2343</v>
+        <v>-9.1776</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3332</v>
+        <v>-0.9696000000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2204</v>
+        <v>10.4927</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9228</v>
+        <v>4.9709</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2976</v>
+        <v>5.5219</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3469</v>
+        <v>-20.6399</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3114</v>
+        <v>-14.1483</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0356</v>
+        <v>-6.4915</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>4.8271</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1585</v>
+        <v>-27.224</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9308</v>
+        <v>32.051</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3416000000000001</v>
+        <v>-2.3456</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2954</v>
+        <v>-3.0276</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9536</v>
+        <v>0.6819000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0845</v>
+        <v>0.4339000000000003</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5712</v>
+        <v>6.782</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6557</v>
+        <v>-6.348100000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GUERRA LOZANO</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.3858</v>
+        <v>-8.413</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.7486</v>
+        <v>-9.152699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.363</v>
+        <v>0.7401</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.1469</v>
+        <v>-16.5003</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.1776</v>
+        <v>-23.6191</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9696000000000002</v>
+        <v>7.119000000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>10.4927</v>
+        <v>7.0343</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9709</v>
+        <v>-6.5017</v>
       </c>
       <c r="L12" t="n">
-        <v>5.5219</v>
+        <v>13.5359</v>
       </c>
       <c r="M12" t="n">
-        <v>-20.6399</v>
+        <v>-23.5345</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.1483</v>
+        <v>-17.1176</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.4915</v>
+        <v>-6.417</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8271</v>
+        <v>12.3571</v>
       </c>
       <c r="Q12" t="n">
-        <v>-27.224</v>
+        <v>-22.5905</v>
       </c>
       <c r="R12" t="n">
-        <v>32.051</v>
+        <v>34.9469</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.4994</v>
+        <v>-8.7926</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.7993</v>
+        <v>-5.9038</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7001000000000002</v>
+        <v>-2.8886</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4339000000000003</v>
+        <v>4.5229</v>
       </c>
       <c r="W12" t="n">
-        <v>6.782</v>
+        <v>12.3067</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.348100000000001</v>
+        <v>-7.7839</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.1976</v>
+        <v>-10.1854</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.1382</v>
+        <v>-11.5336</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.0594</v>
+        <v>1.3483</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.7877</v>
+        <v>-10.3513</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.727399999999999</v>
+        <v>-14.8111</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.0603</v>
+        <v>4.46</v>
       </c>
       <c r="J13" t="n">
-        <v>19.671</v>
+        <v>-1.445</v>
       </c>
       <c r="K13" t="n">
-        <v>22.7072</v>
+        <v>-5.1504</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0363</v>
+        <v>3.7055</v>
       </c>
       <c r="M13" t="n">
-        <v>-44.4588</v>
+        <v>-8.9062</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.4345</v>
+        <v>-9.6609</v>
       </c>
       <c r="O13" t="n">
-        <v>-18.0241</v>
+        <v>0.7546999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>5.406099999999999</v>
+        <v>5.4061</v>
       </c>
       <c r="Q13" t="n">
-        <v>-48.0765</v>
+        <v>-8.8817</v>
       </c>
       <c r="R13" t="n">
-        <v>53.4824</v>
+        <v>14.2878</v>
       </c>
       <c r="S13" t="n">
-        <v>11.6963</v>
+        <v>-0.5723000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9298</v>
+        <v>-0.05149999999999988</v>
       </c>
       <c r="U13" t="n">
-        <v>7.7664</v>
+        <v>-0.5206999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-11.512</v>
+        <v>-4.6678</v>
       </c>
       <c r="W13" t="n">
-        <v>10.3374</v>
+        <v>-1.1552</v>
       </c>
       <c r="X13" t="n">
-        <v>-21.8494</v>
+        <v>-3.5126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.4474</v>
+        <v>-16.023</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.1648</v>
+        <v>-18.5744</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2821</v>
+        <v>2.5513</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.5003</v>
+        <v>-15.9488</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.6191</v>
+        <v>-9.695500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>7.119000000000002</v>
+        <v>-6.253299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0343</v>
+        <v>4.3589</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.5017</v>
+        <v>3.9697</v>
       </c>
       <c r="L14" t="n">
-        <v>13.5359</v>
+        <v>0.3896999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-23.5345</v>
+        <v>-20.3079</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.1176</v>
+        <v>-13.6652</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.417</v>
+        <v>-6.643</v>
       </c>
       <c r="P14" t="n">
-        <v>12.3571</v>
+        <v>4.4408</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.5905</v>
+        <v>-23.5558</v>
       </c>
       <c r="R14" t="n">
-        <v>34.9469</v>
+        <v>27.9961</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.8271</v>
+        <v>-2.6486</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.9159</v>
+        <v>-2.4471</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.9111</v>
+        <v>-0.2014</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5229</v>
+        <v>-1.8662</v>
       </c>
       <c r="W14" t="n">
-        <v>12.3067</v>
+        <v>3.0692</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.7839</v>
+        <v>-4.935300000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ABITBOL VIERA</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.0162</v>
+        <v>-18.8936</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.5127</v>
+        <v>-13.039</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.5032</v>
+        <v>-5.854800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-22.1625</v>
+        <v>-19.7021</v>
       </c>
       <c r="H15" t="n">
-        <v>-13.6776</v>
+        <v>-13.6975</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.4849</v>
+        <v>-6.0048</v>
       </c>
       <c r="J15" t="n">
-        <v>4.414</v>
+        <v>9.771699999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4008999999999996</v>
+        <v>1.4234</v>
       </c>
       <c r="L15" t="n">
-        <v>4.013</v>
+        <v>8.347799999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-26.5765</v>
+        <v>-29.4735</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.0787</v>
+        <v>-15.1212</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.4979</v>
+        <v>-14.3524</v>
       </c>
       <c r="P15" t="n">
-        <v>10.4262</v>
+        <v>3.0892</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.0949</v>
+        <v>-38.4227</v>
       </c>
       <c r="R15" t="n">
-        <v>24.5209</v>
+        <v>41.5116</v>
       </c>
       <c r="S15" t="n">
-        <v>0.06000000000000028</v>
+        <v>-6.3922</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1444999999999996</v>
+        <v>-5.6166</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2045000000000002</v>
+        <v>-0.7758999999999997</v>
       </c>
       <c r="V15" t="n">
-        <v>-10.3399</v>
+        <v>4.1121</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3122</v>
+        <v>21.2288</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.6521</v>
+        <v>-17.1168</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>M. ABITBOL VIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.9252</v>
+        <v>-22.5111</v>
       </c>
       <c r="E16" t="n">
-        <v>-25.6488</v>
+        <v>-8.022500000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2761000000000009</v>
+        <v>-14.4885</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.9488</v>
+        <v>-22.1625</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.695500000000001</v>
+        <v>-13.6776</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.253299999999999</v>
+        <v>-8.4849</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3589</v>
+        <v>4.414</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9697</v>
+        <v>0.4008999999999996</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3896999999999999</v>
+        <v>4.013</v>
       </c>
       <c r="M16" t="n">
-        <v>-20.3079</v>
+        <v>-26.5765</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.6652</v>
+        <v>-14.0787</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.643</v>
+        <v>-12.4979</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4408</v>
+        <v>10.4262</v>
       </c>
       <c r="Q16" t="n">
-        <v>-23.5558</v>
+        <v>-14.0949</v>
       </c>
       <c r="R16" t="n">
-        <v>27.9961</v>
+        <v>24.5209</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.5504</v>
+        <v>-0.4346999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.521699999999999</v>
+        <v>-1.6541</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.029</v>
+        <v>1.2193</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8662</v>
+        <v>-10.3399</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0692</v>
+        <v>3.3122</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.935300000000001</v>
+        <v>-13.6521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>-26.5799</v>
+        <v>-25.5475</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.4175</v>
+        <v>-10.1172</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.1622</v>
+        <v>-15.4306</v>
       </c>
       <c r="G17" t="n">
-        <v>-19.7021</v>
+        <v>-24.4146</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.6975</v>
+        <v>-26.2976</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.0048</v>
+        <v>1.882900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>9.771699999999999</v>
+        <v>9.6677</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4234</v>
+        <v>-6.0065</v>
       </c>
       <c r="L17" t="n">
-        <v>8.347799999999999</v>
+        <v>15.6744</v>
       </c>
       <c r="M17" t="n">
-        <v>-29.4735</v>
+        <v>-34.0825</v>
       </c>
       <c r="N17" t="n">
-        <v>-15.1212</v>
+        <v>-20.291</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.3524</v>
+        <v>-13.7916</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0892</v>
+        <v>-9.654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-38.4227</v>
+        <v>-47.3042</v>
       </c>
       <c r="R17" t="n">
-        <v>41.5116</v>
+        <v>37.6501</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.0787</v>
+        <v>-12.1922</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.9953</v>
+        <v>-6.9456</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.0834</v>
+        <v>-5.2467</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1121</v>
+        <v>20.7128</v>
       </c>
       <c r="W17" t="n">
-        <v>21.2288</v>
+        <v>34.4647</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.1168</v>
+        <v>-13.7521</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-32.2757</v>
+        <v>-28.7131</v>
       </c>
       <c r="E18" t="n">
-        <v>-25.3385</v>
+        <v>-20.4979</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.9373</v>
+        <v>-8.215100000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-27.7553</v>
@@ -1858,13 +1858,13 @@
         <v>56.1857</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.7827</v>
+        <v>-4.2199</v>
       </c>
       <c r="T18" t="n">
-        <v>-10.3554</v>
+        <v>-5.5149</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5727</v>
+        <v>1.2947</v>
       </c>
       <c r="V18" t="n">
         <v>9.2477</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-37.5572</v>
+        <v>-30.3559</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.1089</v>
+        <v>-20.3708</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.4486</v>
+        <v>-9.985000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-24.4146</v>
+        <v>-24.7877</v>
       </c>
       <c r="H19" t="n">
-        <v>-26.2976</v>
+        <v>-3.727399999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.882900000000001</v>
+        <v>-21.0603</v>
       </c>
       <c r="J19" t="n">
-        <v>9.6677</v>
+        <v>19.671</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.0065</v>
+        <v>22.7072</v>
       </c>
       <c r="L19" t="n">
-        <v>15.6744</v>
+        <v>-3.0363</v>
       </c>
       <c r="M19" t="n">
-        <v>-34.0825</v>
+        <v>-44.4588</v>
       </c>
       <c r="N19" t="n">
-        <v>-20.291</v>
+        <v>-26.4345</v>
       </c>
       <c r="O19" t="n">
-        <v>-13.7916</v>
+        <v>-18.0241</v>
       </c>
       <c r="P19" t="n">
-        <v>-9.654</v>
+        <v>5.406099999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-47.3042</v>
+        <v>-48.0765</v>
       </c>
       <c r="R19" t="n">
-        <v>37.6501</v>
+        <v>53.4824</v>
       </c>
       <c r="S19" t="n">
-        <v>-24.2017</v>
+        <v>0.5379000000000002</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.9373</v>
+        <v>-2.3026</v>
       </c>
       <c r="U19" t="n">
-        <v>-10.2647</v>
+        <v>2.8405</v>
       </c>
       <c r="V19" t="n">
-        <v>20.7128</v>
+        <v>-11.512</v>
       </c>
       <c r="W19" t="n">
-        <v>34.4647</v>
+        <v>10.3374</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.7521</v>
+        <v>-21.8494</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>-41.6257</v>
+        <v>-40.1384</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.5002</v>
+        <v>-27.2996</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.1257</v>
+        <v>-12.839</v>
       </c>
       <c r="G20" t="n">
         <v>-15.6632</v>
@@ -2014,13 +2014,13 @@
         <v>31.6648</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8121000000000003</v>
+        <v>0.6752</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2395000000000004</v>
+        <v>-0.5600999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0513</v>
+        <v>1.2354</v>
       </c>
       <c r="V20" t="n">
         <v>-5.456399999999999</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-225.0676</v>
+        <v>-203.2761</v>
       </c>
       <c r="E21" t="n">
-        <v>-158.4874</v>
+        <v>-149.107</v>
       </c>
       <c r="F21" t="n">
-        <v>-66.57989999999999</v>
+        <v>-54.1695</v>
       </c>
       <c r="G21" t="n">
         <v>-194.0616</v>
@@ -2062,7 +2062,7 @@
         <v>-127.9009</v>
       </c>
       <c r="I21" t="n">
-        <v>-66.1611</v>
+        <v>-66.16109999999999</v>
       </c>
       <c r="J21" t="n">
         <v>104.9662</v>
@@ -2092,16 +2092,16 @@
         <v>379.3977</v>
       </c>
       <c r="S21" t="n">
-        <v>-45.1023</v>
+        <v>-23.3112</v>
       </c>
       <c r="T21" t="n">
-        <v>-35.6759</v>
+        <v>-26.2948</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.426599999999999</v>
+        <v>2.9837</v>
       </c>
       <c r="V21" t="n">
-        <v>3.478500000000001</v>
+        <v>3.478499999999999</v>
       </c>
       <c r="W21" t="n">
         <v>141.0008</v>
